--- a/data/trans_orig/IP19C06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C06-Estudios-trans_orig.xlsx
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>242867</t>
+          <t>242558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>471242</t>
+          <t>471401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70139</t>
+          <t>69200</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145323</t>
+          <t>145284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>357895</t>
+          <t>357730</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707436</t>
+          <t>708139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212779</t>
+          <t>213094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219211</t>
+          <t>219349</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235842</t>
+          <t>235830</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452185</t>
+          <t>451738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>459644</t>
+          <t>459377</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79103</t>
+          <t>77853</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163463</t>
+          <t>163955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>346655</t>
+          <t>346712</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352864</t>
+          <t>352863</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>359882</t>
+          <t>359796</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365984</t>
+          <t>365380</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,99%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709607</t>
+          <t>709681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717488</t>
+          <t>717473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24724</t>
+          <t>25051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46308</t>
+          <t>46793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247683</t>
+          <t>247811</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>500119</t>
+          <t>499629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357974</t>
+          <t>357644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>364488</t>
+          <t>364495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>724482</t>
+          <t>724651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>730007</t>
+          <t>730014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>26139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51433</t>
+          <t>51703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>423</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>256820</t>
+          <t>257033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>261403</t>
+          <t>261404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317024</t>
+          <t>316456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>576715</t>
+          <t>576272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>583900</t>
+          <t>584157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92655</t>
+          <t>92260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99002</t>
+          <t>98906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130711</t>
+          <t>131201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226213</t>
+          <t>227171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234350</t>
+          <t>234254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>381139</t>
+          <t>380540</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>388976</t>
+          <t>388868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>475886</t>
+          <t>475881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>860680</t>
+          <t>860933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>871797</t>
+          <t>871994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C06-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>46926</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,107 +1066,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3165</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2874</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2644</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>245198</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>243073</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,79%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>245198</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>242558</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>714</t>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>471401</t>
+          <t>471171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,107 +1409,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3917</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3516</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72422</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69638</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>72422</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>69200</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>217</t>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145284</t>
+          <t>145300</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,107 +1752,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4350</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4001</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4387</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4522</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>360512</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>357381</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>360512</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>357730</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1065</t>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708139</t>
+          <t>708274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2439,47 +2439,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>47964</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1481</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4655</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1129</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7384</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7409</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1481</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5083</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>239432</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>236258</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>217248</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>213094</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>219349</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>213069</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>219206</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>239432</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>235830</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>451738</t>
+          <t>451464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>459377</t>
+          <t>459349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3156</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>742</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4272</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4099</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>742</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>81383</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>78969</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,16%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>81383</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>77853</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,8%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>237</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163955</t>
+          <t>163574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6517</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1128</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7279</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7087</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6206</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>363779</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>359485</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>365386</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>350761</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>346712</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>352863</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>346904</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>352849</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>363779</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>359796</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>365380</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1020</t>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709681</t>
+          <t>710078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717473</t>
+          <t>717580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,107 +3929,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3540</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3487</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27441</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25217</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,51%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,61%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>27441</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25051</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>89,02%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>72</t>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46793</t>
+          <t>46740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,107 +4272,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4929</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4588</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4739</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5280</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -4385,74 +4385,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>368</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>251352</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>247811</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>248152</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>715</t>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>499629</t>
+          <t>500170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>370</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4728,47 +4728,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>87740</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,107 +4958,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3503</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4974</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3513</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5556</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2088</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5975</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -5071,107 +5071,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>367308</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>364505</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>361230</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>357644</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>357200</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>367308</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>364495</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>728538</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>725070</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>730626</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>728538</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>724651</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>730014</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,107 +5532,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3591</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3484</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4079</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>28985</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26139</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>25840</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23159</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26643</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>86,92%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25484</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>67</t>
@@ -5720,27 +5720,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>54469</t>
+          <t>50130</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51703</t>
+          <t>46854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3445</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1648</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4794</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>367</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>308904</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>306100</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,79%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>364</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>260179</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>257033</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>261404</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>321683</t>
+          <t>264532</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316456</t>
+          <t>261519</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>265685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>581862</t>
+          <t>573437</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>576272</t>
+          <t>569874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>584157</t>
+          <t>574941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5587</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3365</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1170</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7816</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>126296</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>121673</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>96711</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>92260</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>98906</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>134900</t>
+          <t>100216</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131201</t>
+          <t>95978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>102433</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>231611</t>
+          <t>226511</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>227171</t>
+          <t>221174</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234254</t>
+          <t>229207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5834</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5758</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2765</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11093</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15143</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>459490</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>455261</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>545</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>385875</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>380540</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>388868</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>482067</t>
+          <t>390589</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>475881</t>
+          <t>385827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>393489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>867941</t>
+          <t>850078</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>860933</t>
+          <t>844844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>871994</t>
+          <t>853785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
